--- a/data/trans_orig/IP26C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP26C_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2007 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2007 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42600</t>
+          <t>43131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47696</t>
+          <t>47140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55859</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94293</t>
+          <t>93787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104518</t>
+          <t>104025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95611</t>
+          <t>95273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>104152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184497</t>
+          <t>184273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197294</t>
+          <t>197928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>55348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111851</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124892</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>63794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118662</t>
+          <t>119425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134403</t>
+          <t>134216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49964</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43014</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52208</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86596</t>
+          <t>86978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99895</t>
+          <t>99491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118621</t>
+          <t>118678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116730</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127964</t>
+          <t>127992</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227362</t>
+          <t>227311</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243905</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>30541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>139636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150995</t>
+          <t>150381</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146483</t>
+          <t>147018</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156494</t>
+          <t>156703</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>290057</t>
+          <t>290041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304604</t>
+          <t>304662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>92845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165722</t>
+          <t>164698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2012 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99698</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111725</t>
+          <t>111852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92633</t>
+          <t>92108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>97581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106408</t>
+          <t>106019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193741</t>
+          <t>193824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204976</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>29926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62324</t>
+          <t>61820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109351</t>
+          <t>108828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122889</t>
+          <t>123055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75693</t>
+          <t>75560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80235</t>
+          <t>80212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147656</t>
+          <t>147224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154760</t>
+          <t>154922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>80666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83259</t>
+          <t>82854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>32441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>55472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>105384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120962</t>
+          <t>120287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113024</t>
+          <t>114044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127671</t>
+          <t>127843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225024</t>
+          <t>226159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>245213</t>
+          <t>245434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>35172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143999</t>
+          <t>144753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154935</t>
+          <t>155472</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148446</t>
+          <t>148967</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159991</t>
+          <t>160398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>297000</t>
+          <t>296081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>313090</t>
+          <t>312961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87534</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>68057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96061</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174051</t>
+          <t>174286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2016 (tasa de respuesta: 99,01%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2016 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105465</t>
+          <t>104155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>115237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>34590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84191</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95130</t>
+          <t>94810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>88861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101055</t>
+          <t>100714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177598</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193024</t>
+          <t>192777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56529</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>63894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59765</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>67099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>118431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128888</t>
+          <t>129344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63977</t>
+          <t>63331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72265</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>64201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74110</t>
+          <t>74244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131537</t>
+          <t>130644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144627</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85818</t>
+          <t>85650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50090</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52944</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106212</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>111376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117249</t>
+          <t>117026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128673</t>
+          <t>128338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118691</t>
+          <t>119155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>131192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>240104</t>
+          <t>240116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256746</t>
+          <t>256339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135021</t>
+          <t>134280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>148313</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143145</t>
+          <t>143584</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156656</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282489</t>
+          <t>282628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301491</t>
+          <t>301974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>78190</t>
+          <t>78767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>117201</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>152569</t>
+          <t>152216</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han tenido una quemadura en el último año en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71932</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>78763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151886</t>
+          <t>151933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116308</t>
+          <t>115700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124129</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115388</t>
+          <t>115164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>126498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235529</t>
+          <t>235752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248947</t>
+          <t>248683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>56395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>65170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118823</t>
+          <t>118928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76742</t>
+          <t>77190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129488</t>
+          <t>129572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>142878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>66174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>72974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>59430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>74633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109748</t>
+          <t>109690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>119590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132329</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146461</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247630</t>
+          <t>247319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263071</t>
+          <t>263189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56629</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>108472</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120926</t>
+          <t>120979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120675</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136601</t>
+          <t>136279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231785</t>
+          <t>231632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253886</t>
+          <t>254146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>123542</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>166277</t>
+          <t>165872</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
